--- a/input/test-load.xlsx
+++ b/input/test-load.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GabGren\Work Folders\Documents\Projektmappar\E-Mats\repo_official\Transmogrifier\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GabGren\Work Folders\Documents\Projektmappar\E-Mats\repo_official\Transmogrifier\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A397D03-A56A-4819-9435-E013D4C7A944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEBFA4E-CDE1-4457-970B-FF441F853160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -468,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -484,7 +484,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>200</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -508,7 +508,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>200</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -524,7 +524,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -532,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -548,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -564,7 +564,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -572,7 +572,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -580,7 +580,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>200</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -588,7 +588,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -596,7 +596,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>200</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -604,7 +604,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -612,7 +612,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>200</v>
+        <v>850</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -620,7 +620,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -628,7 +628,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
